--- a/Indian_Banking_data.xlsx
+++ b/Indian_Banking_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Online_Class_Tools\Data_Analyst\Notes\Module_05_Excel\Project\Indian Banking Transactions Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Innomatics\Git_Uploads\Nope\banking-transactions-analysis-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287CA511-C4F6-40B7-8657-0905C1C3BC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102189C1-CD05-443F-9ECD-C7D665E42B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3520,6 +3520,12 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
+      <numFmt numFmtId="35" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color indexed="64"/>
@@ -3545,14 +3551,13 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFE9E17F"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -4147,7 +4152,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="dk1"/>
                 </a:solidFill>
@@ -4203,7 +4208,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="dk1"/>
                 </a:solidFill>
@@ -5858,7 +5863,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="dk1"/>
                 </a:solidFill>
@@ -5914,7 +5919,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="dk1"/>
                 </a:solidFill>
@@ -6891,7 +6896,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -7559,7 +7564,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -9846,7 +9851,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="dk1"/>
                 </a:solidFill>
@@ -9902,7 +9907,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="dk1"/>
                 </a:solidFill>
@@ -13259,13 +13264,13 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent2"/>
         </a:lnRef>
         <a:fillRef idx="2">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent2"/>
         </a:fillRef>
         <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent2"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="dk1"/>
@@ -13322,6 +13327,12 @@
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="1">
@@ -13447,19 +13458,14 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>380999</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>11775</xdr:rowOff>
+      <xdr:rowOff>11774</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>373742</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>120313</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="7366937" cy="3417226"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="10" name="Rectangle: Rounded Corners 9">
@@ -13473,8 +13479,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="380999" y="1031872"/>
-          <a:ext cx="7366937" cy="3426925"/>
+          <a:off x="380999" y="1031871"/>
+          <a:ext cx="7366937" cy="3417226"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13483,25 +13489,30 @@
         </a:prstGeom>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent6"/>
         </a:lnRef>
-        <a:fillRef idx="2">
-          <a:schemeClr val="accent1"/>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent6"/>
         </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent6"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
           <a:endParaRPr lang="en-IN" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
             <a:effectLst>
               <a:outerShdw blurRad="50800" dist="571500" dir="18900000" algn="bl" rotWithShape="0">
                 <a:prstClr val="black">
@@ -13514,7 +13525,7 @@
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
@@ -13552,16 +13563,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent3"/>
         </a:lnRef>
-        <a:fillRef idx="2">
-          <a:schemeClr val="accent1"/>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent3"/>
         </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent3"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -13620,13 +13631,13 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent4"/>
         </a:lnRef>
         <a:fillRef idx="2">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent4"/>
         </a:fillRef>
         <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent4"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="dk1"/>
@@ -13839,17 +13850,17 @@
         </a:prstGeom>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent5"/>
         </a:lnRef>
-        <a:fillRef idx="2">
-          <a:schemeClr val="accent1"/>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent5"/>
         </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
+        <a:effectRef idx="3">
+          <a:schemeClr val="accent5"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -13857,12 +13868,16 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-IN" sz="1100" b="1">
+          <a:endParaRPr lang="en-IN" sz="1100" b="0" cap="none" spc="0">
+            <a:ln w="0"/>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
             <a:effectLst>
-              <a:outerShdw blurRad="50800" dist="571500" dir="18900000" algn="bl" rotWithShape="0">
-                <a:prstClr val="black">
-                  <a:alpha val="40000"/>
-                </a:prstClr>
+              <a:outerShdw blurRad="38100" dist="25400" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="6E747A">
+                  <a:alpha val="43000"/>
+                </a:srgbClr>
               </a:outerShdw>
             </a:effectLst>
           </a:endParaRPr>
@@ -26412,689 +26427,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B8E0B43A-2772-47AF-987C-BD541F985A7B}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="M3:N29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="26">
-        <item x="2"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item x="4"/>
-        <item x="23"/>
-        <item x="17"/>
-        <item x="14"/>
-        <item x="12"/>
-        <item x="22"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="15"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="21"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="10"/>
-        <item x="16"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="24"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="26">
-        <item x="2"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item x="4"/>
-        <item x="23"/>
-        <item x="17"/>
-        <item x="14"/>
-        <item x="12"/>
-        <item x="22"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="15"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="21"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="10"/>
-        <item x="16"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="24"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item x="10"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="26">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Transaction ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="2" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{551EF503-4C7D-48A2-9A7B-039EF54DF977}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="E20:K47" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="26">
-        <item x="2"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item x="4"/>
-        <item x="23"/>
-        <item x="17"/>
-        <item x="14"/>
-        <item x="12"/>
-        <item x="22"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="15"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="21"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="10"/>
-        <item x="16"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="24"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="26">
-        <item x="2"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item x="4"/>
-        <item x="23"/>
-        <item x="17"/>
-        <item x="14"/>
-        <item x="12"/>
-        <item x="22"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="15"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="21"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="10"/>
-        <item x="16"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="24"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item x="10"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="26">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="4"/>
-  </colFields>
-  <colItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Fraud Flag" fld="18" baseField="6" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="1">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="0">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="5">
-    <chartFormat chart="2" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="11" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="14" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1F6A33B-51CA-4D02-8C31-769BF63E82F4}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
-  <location ref="P3:R8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="26">
-        <item x="2"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item x="4"/>
-        <item x="23"/>
-        <item x="17"/>
-        <item x="14"/>
-        <item x="12"/>
-        <item x="22"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="15"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="21"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="10"/>
-        <item x="16"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="24"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item x="10"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Count of Transaction ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Sum of Transaction Amount" fld="9" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="4">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{70A67AAF-9D18-40A8-94F8-8531FDFB2915}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="E3:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="19">
@@ -27243,14 +26575,14 @@
     <dataField name="Sum of Transaction Amount" fld="9" baseField="0" baseItem="0" numFmtId="43"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="3">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="16" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="0">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -27328,7 +26660,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0468FF78-8BCD-4891-9081-5AAFFB2643B9}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="P20:Q25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -28006,7 +27338,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1F4E5CF3-F9DD-48EA-8E25-6C73E980BA31}" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="P11:Q17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -28708,7 +28040,528 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B8E0B43A-2772-47AF-987C-BD541F985A7B}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="M3:N29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="26">
+        <item x="2"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item x="4"/>
+        <item x="23"/>
+        <item x="17"/>
+        <item x="14"/>
+        <item x="12"/>
+        <item x="22"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="15"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="10"/>
+        <item x="16"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="24"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="26">
+        <item x="2"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item x="4"/>
+        <item x="23"/>
+        <item x="17"/>
+        <item x="14"/>
+        <item x="12"/>
+        <item x="22"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="15"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="10"/>
+        <item x="16"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="24"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="11"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="10"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="26">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Transaction ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{551EF503-4C7D-48A2-9A7B-039EF54DF977}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="E20:K47" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="26">
+        <item x="2"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item x="4"/>
+        <item x="23"/>
+        <item x="17"/>
+        <item x="14"/>
+        <item x="12"/>
+        <item x="22"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="15"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="10"/>
+        <item x="16"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="24"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="26">
+        <item x="2"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item x="4"/>
+        <item x="23"/>
+        <item x="17"/>
+        <item x="14"/>
+        <item x="12"/>
+        <item x="22"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="15"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="10"/>
+        <item x="16"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="24"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="11"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="10"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="26">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Fraud Flag" fld="18" baseField="6" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="3">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="5">
+    <chartFormat chart="2" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{44D9F422-9745-4254-BB69-DC7464075E5E}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="B3:C9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -29342,6 +29195,168 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1F6A33B-51CA-4D02-8C31-769BF63E82F4}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
+  <location ref="P3:R8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="26">
+        <item x="2"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item x="4"/>
+        <item x="23"/>
+        <item x="17"/>
+        <item x="14"/>
+        <item x="12"/>
+        <item x="22"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="15"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="10"/>
+        <item x="16"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="24"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="11"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="10"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Count of Transaction ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Transaction Amount" fld="9" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Year" xr10:uid="{4EC0C290-DBB4-4684-87B3-0A598C539F1D}" sourceName="Year">
   <pivotTables>
@@ -29438,9 +29453,9 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Year" xr10:uid="{CF38400C-4E33-4D6E-9E23-527312EF6C91}" cache="Slicer_Year" caption="Year" style="SlicerStyleDark1" rowHeight="234950"/>
-  <slicer name="Month" xr10:uid="{002FD744-323A-4975-9969-49EBC37A1A9B}" cache="Slicer_Month" caption="Month" style="SlicerStyleDark1" rowHeight="234950"/>
-  <slicer name="City" xr10:uid="{C1CEEF2D-C961-4185-833D-7989B2447464}" cache="Slicer_City" caption="City" style="SlicerStyleDark1" rowHeight="234950"/>
+  <slicer name="Year" xr10:uid="{CF38400C-4E33-4D6E-9E23-527312EF6C91}" cache="Slicer_Year" caption="Year" style="SlicerStyleLight4" rowHeight="234950"/>
+  <slicer name="Month" xr10:uid="{002FD744-323A-4975-9969-49EBC37A1A9B}" cache="Slicer_Month" caption="Month" style="SlicerStyleDark4" rowHeight="234950"/>
+  <slicer name="City" xr10:uid="{C1CEEF2D-C961-4185-833D-7989B2447464}" cache="Slicer_City" caption="City" style="SlicerStyleDark4" rowHeight="234950"/>
 </slicers>
 </file>
 
